--- a/artfynd/A 32097-2025 artfynd.xlsx
+++ b/artfynd/A 32097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028777</v>
       </c>
       <c r="B2" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127028782</v>
       </c>
       <c r="B3" t="n">
-        <v>98382</v>
+        <v>98457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127028775</v>
       </c>
       <c r="B4" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127028771</v>
       </c>
       <c r="B5" t="n">
-        <v>80112</v>
+        <v>80143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127028763</v>
       </c>
       <c r="B6" t="n">
-        <v>91263</v>
+        <v>91337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2025 artfynd.xlsx
+++ b/artfynd/A 32097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028777</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127028782</v>
       </c>
       <c r="B3" t="n">
-        <v>98457</v>
+        <v>98463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127028775</v>
       </c>
       <c r="B4" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127028771</v>
       </c>
       <c r="B5" t="n">
-        <v>80143</v>
+        <v>80146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127028763</v>
       </c>
       <c r="B6" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2025 artfynd.xlsx
+++ b/artfynd/A 32097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028777</v>
       </c>
       <c r="B2" t="n">
-        <v>98465</v>
+        <v>98466</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127028782</v>
       </c>
       <c r="B3" t="n">
-        <v>98463</v>
+        <v>98464</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127028763</v>
       </c>
       <c r="B6" t="n">
-        <v>91343</v>
+        <v>91344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2025 artfynd.xlsx
+++ b/artfynd/A 32097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028777</v>
       </c>
       <c r="B2" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127028782</v>
       </c>
       <c r="B3" t="n">
-        <v>98464</v>
+        <v>98468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127028775</v>
       </c>
       <c r="B4" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127028771</v>
       </c>
       <c r="B5" t="n">
-        <v>80146</v>
+        <v>80150</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127028763</v>
       </c>
       <c r="B6" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2025 artfynd.xlsx
+++ b/artfynd/A 32097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028777</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127028782</v>
       </c>
       <c r="B3" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2025 artfynd.xlsx
+++ b/artfynd/A 32097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028777</v>
       </c>
       <c r="B2" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127028782</v>
       </c>
       <c r="B3" t="n">
-        <v>98469</v>
+        <v>98471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127028775</v>
       </c>
       <c r="B4" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127028771</v>
       </c>
       <c r="B5" t="n">
-        <v>80150</v>
+        <v>80152</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127028763</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2025 artfynd.xlsx
+++ b/artfynd/A 32097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028777</v>
       </c>
       <c r="B2" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127028782</v>
       </c>
       <c r="B3" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127028763</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2025 artfynd.xlsx
+++ b/artfynd/A 32097-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127028777</v>
       </c>
       <c r="B2" t="n">
-        <v>98479</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127028782</v>
       </c>
       <c r="B3" t="n">
-        <v>98477</v>
+        <v>98457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>127028775</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>127028771</v>
       </c>
       <c r="B5" t="n">
-        <v>80152</v>
+        <v>80143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>127028763</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>91337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 32097-2025 artfynd.xlsx
+++ b/artfynd/A 32097-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127028777</v>
+        <v>127028775</v>
       </c>
       <c r="B2" t="n">
-        <v>98479</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459776</v>
+        <v>459779</v>
       </c>
       <c r="R2" t="n">
-        <v>6989529</v>
+        <v>6989580</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127028782</v>
+        <v>127028771</v>
       </c>
       <c r="B3" t="n">
-        <v>98477</v>
+        <v>80461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459711</v>
+        <v>459838</v>
       </c>
       <c r="R3" t="n">
-        <v>6989587</v>
+        <v>6989579</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127028775</v>
+        <v>127028777</v>
       </c>
       <c r="B4" t="n">
-        <v>80123</v>
+        <v>99142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459779</v>
+        <v>459776</v>
       </c>
       <c r="R4" t="n">
-        <v>6989580</v>
+        <v>6989529</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127028771</v>
+        <v>127028782</v>
       </c>
       <c r="B5" t="n">
-        <v>80152</v>
+        <v>99140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459838</v>
+        <v>459711</v>
       </c>
       <c r="R5" t="n">
-        <v>6989579</v>
+        <v>6989587</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1060,103 +1060,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>127028763</v>
-      </c>
-      <c r="B6" t="n">
-        <v>91356</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Rammflon, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>459848</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6989448</v>
-      </c>
-      <c r="S6" t="n">
-        <v>25</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Marby</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Klas Andersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32097-2025 artfynd.xlsx
+++ b/artfynd/A 32097-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028775</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028771</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028777</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028782</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>